--- a/deliverables/qc_gap_analysis/tracker/CoQ_Master_Register_2026-09-17.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/CoQ_Master_Register_2026-09-17.xlsx
@@ -4102,7 +4102,7 @@
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -12022,7 +12022,7 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
@@ -27143,7 +27143,7 @@
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -35811,7 +35811,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
